--- a/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">

--- a/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Features</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+          <t>h_01KKXFEP8K9H5STEX8HPYZRNVX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KKXFEP8K9H5STEX8HPYZRNVX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,41 +495,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,41 +539,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,41 +583,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integration Features</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,63 +627,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KHK1CAS2QHGYWZN7TPET5E8D</t>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK1CAS2QHGYWZN7TPET5E8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manage Hires</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KHK210EF6PMW6J4GA9H9GS9C</t>
+          <t>h_01KHK1CAS2QHGYWZN7TPET5E8D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK210EF6PMW6J4GA9H9GS9C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK1CAS2QHGYWZN7TPET5E8D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Onboarding Tickets Generation</t>
+          <t>Manage Hires</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KHK2155TJ64WEF1N7ASAXCEZ</t>
+          <t>h_01KHK210EF6PMW6J4GA9H9GS9C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK2155TJ64WEF1N7ASAXCEZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK210EF6PMW6J4GA9H9GS9C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Onboarding Tickets Generation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,63 +693,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KHK22304N44RG4GH3VW8EBG3</t>
+          <t>h_01KHK2155TJ64WEF1N7ASAXCEZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK22304N44RG4GH3VW8EBG3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK2155TJ64WEF1N7ASAXCEZ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Terminations</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KHKACRS1SACB85DEV28Y1RTF</t>
+          <t>h_01KHK22304N44RG4GH3VW8EBG3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKACRS1SACB85DEV28Y1RTF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHK22304N44RG4GH3VW8EBG3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Offboarding Tickets Generation</t>
+          <t>Manage Terminations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHKADH0CYDDWB04HGJNJNS4F</t>
+          <t>h_01KHKACRS1SACB85DEV28Y1RTF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKADH0CYDDWB04HGJNJNS4F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKACRS1SACB85DEV28Y1RTF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Offboarding Tickets Generation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,151 +759,151 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHKADH0CMR3ZG14R5C65TJTW</t>
+          <t>h_01KHKADH0CYDDWB04HGJNJNS4F</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKADH0CMR3ZG14R5C65TJTW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKADH0CYDDWB04HGJNJNS4F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Date Offset</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
+          <t>h_01KHKADH0CMR3ZG14R5C65TJTW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKADH0CMR3ZG14R5C65TJTW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Onboarding Date Offset</t>
+          <t>Additional Instances</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHKANS7965H6AX88QT0E48QG</t>
+          <t>h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKANS7965H6AX88QT0E48QG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Offboarding Date Offset</t>
+          <t>Date Offset</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
+          <t>h_01KKXJ8AD67T2GXC8K53KGPE9M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KKXJ8AD67T2GXC8K53KGPE9M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Onboarding Date Offset</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
+          <t>h_01KHKANS7965H6AX88QT0E48QG</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKANS7965H6AX88QT0E48QG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Offboarding Date Offset</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KHKBGVW1RE1DJZYENEJ6SM78</t>
+          <t>h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBGVW1RE1DJZYENEJ6SM78</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Onboarding Map</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>h_01KHKBGVW1RE1DJZYENEJ6SM78</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBGVW1RE1DJZYENEJ6SM78</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Offboarding Map</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>h_01KKXF14DDD398N247JXNJ6WD6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KKXF14DDD398N247JXNJ6WD6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,76 +957,142 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Onboarding Map</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Offboarding Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,51 +947,51 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>h_01KKXKNHW297KGFRCENNAR6GMR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KKXKNHW297KGFRCENNAR6GMR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Onboarding Map</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Offboarding Map</t>
+          <t>Onboarding Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,63 +1001,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Offboarding Map</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,32 +1067,54 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,73 +991,73 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Onboarding Map</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Offboarding Map</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,54 +1067,10 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ServiceNow-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
